--- a/data/trending_integrated_20261013_12.xlsx
+++ b/data/trending_integrated_20261013_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F2" t="n">
         <v>70</v>
       </c>
       <c r="G2" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87161347450</v>
+        <v>87201472050</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 및 지역 개발 수혜 기대감. 연상 랠리 및 대장주로서의 강세 전망.</t>
+          <t>호남 반도체 투자 및 경제자유구역 확대 수혜 기대, 연속 상한가 및 10연상 랠리 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남 반도체', '수혜주', '연상']</t>
+          <t>['호남반도체', '경제자유구역', '10연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,18 +659,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18400</v>
+        <v>18380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.54%</t>
+          <t>'+12.42%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
         <v>82</v>
@@ -702,7 +702,7 @@
         <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>217679660070</v>
+        <v>219658329635</v>
       </c>
       <c r="P3" t="n">
         <v>19930</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>보안 기술 중요성 부각과 함께 신고가 경신 및 추가 상승 기대감. 해킹 관련 이슈 언급.</t>
+          <t>보안 기술 및 AI 관련 언급, 신고가 돌파 및 상승 기대감. 프랑스 국채 불안 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안', '신고가', '해킹']</t>
+          <t>['보안주', 'AI', '신고가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12320</v>
+        <v>12290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.29%</t>
+          <t>'+11.02%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>157</v>
       </c>
       <c r="F4" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G4" t="n">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>298228407760</v>
+        <v>300212331590</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>급등락 속 주포의 물량 확보 및 추가 상승 기대감. 일부 테마 영향력 축소.</t>
+          <t>주가 급등 및 물량 소화 중, 호남 클러스터 외 테마 죽음. "인생역전 주식" 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주포', '테마', '물량']</t>
+          <t>['호남클러스터', '물갈이', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1621</v>
+        <v>1599</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.72%</t>
+          <t>'+1.33%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H5" t="n">
         <v>0.32</v>
@@ -886,7 +886,7 @@
         <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>8310590302</v>
+        <v>8422909799</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13300</v>
+        <v>13220</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.82%</t>
+          <t>'-1.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F6" t="n">
         <v>78</v>
       </c>
       <c r="G6" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H6" t="n">
         <v>0.3</v>
@@ -978,7 +978,7 @@
         <v>0.21</v>
       </c>
       <c r="O6" t="n">
-        <v>58401685315</v>
+        <v>59349847410</v>
       </c>
       <c r="P6" t="n">
         <v>28700</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가 부양 시도와 매도세 충돌. 공매도 및 대차 관련 언급에도 상승 동력 부족.</t>
+          <t>공매도 세력에 대한 경계, 리보&amp;캄렐 간암 1차 승인 기대감. 통합 IR 데이 주목.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '매수세']</t>
+          <t>['공매도', '리보', '캄렐']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43600</v>
+        <v>43550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-1.91%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.23</v>
       </c>
       <c r="E7" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F7" t="n">
         <v>103</v>
       </c>
       <c r="G7" t="n">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="H7" t="n">
         <v>13.1</v>
@@ -1070,7 +1070,7 @@
         <v>13.33</v>
       </c>
       <c r="O7" t="n">
-        <v>21626263050</v>
+        <v>22307099975</v>
       </c>
       <c r="P7" t="n">
         <v>69200</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신약 승인 기대감 속 공매도 세력 경계 및 주가 상승 가능성 언급. 악재 발생 시 하락 가능성도 제기.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 182건 토론 포착</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신약', '공매도', '승인']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6060</v>
+        <v>6080</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.42%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1162,7 +1162,7 @@
         <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>21784048240</v>
+        <v>22028746825</v>
       </c>
       <c r="P8" t="n">
         <v>11370</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13070</v>
+        <v>18040</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.46%</t>
+          <t>'-2.75%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.01</v>
+        <v>-0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>293</v>
+        <v>89</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13400</v>
+        <v>18550</v>
       </c>
       <c r="K9" t="n">
-        <v>13750</v>
+        <v>17550</v>
       </c>
       <c r="L9" t="n">
-        <v>15390</v>
+        <v>19580</v>
       </c>
       <c r="M9" t="n">
-        <v>12380</v>
+        <v>17010</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="O9" t="n">
-        <v>172079661590</v>
+        <v>68571756800</v>
       </c>
       <c r="P9" t="n">
-        <v>19380</v>
+        <v>30550</v>
       </c>
       <c r="Q9" t="n">
-        <v>3200</v>
+        <v>6100</v>
       </c>
       <c r="R9" t="n">
-        <v>-76000</v>
+        <v>-65000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>반도체 클러스터 투자 관련 언급과 함께 주가 부진에 대한 답답함 토로. 공매도 경계.</t>
+          <t>해킹 관련 이슈에도 지수 및 보안주 흐름에 따라 변동성 예상. 기대감 속 투자자 간 의견 분분.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '클러스터', '공매도']</t>
+          <t>['해킹', '보안주', '폭락']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,77 +1292,77 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18000</v>
+        <v>12920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.96%</t>
+          <t>'-3.58%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.42</v>
+        <v>-1.01</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="G10" t="n">
-        <v>92</v>
+        <v>309</v>
       </c>
       <c r="H10" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18550</v>
+        <v>13400</v>
       </c>
       <c r="K10" t="n">
-        <v>17550</v>
+        <v>13750</v>
       </c>
       <c r="L10" t="n">
-        <v>19580</v>
+        <v>15390</v>
       </c>
       <c r="M10" t="n">
-        <v>17010</v>
+        <v>12380</v>
       </c>
       <c r="N10" t="n">
-        <v>0.88</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>68153030130</v>
+        <v>173047253770</v>
       </c>
       <c r="P10" t="n">
-        <v>30550</v>
+        <v>19380</v>
       </c>
       <c r="Q10" t="n">
-        <v>6100</v>
+        <v>3200</v>
       </c>
       <c r="R10" t="n">
-        <v>-65000</v>
+        <v>-76000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 상황 속 보안주 급등 기대감. 라온시큐어와 비교 언급.</t>
+          <t>호남 반도체 투자 관련 언급, 주가 상승 기대감 및 주포 움직임 주시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', '급등']</t>
+          <t>['호남반도체', '속도전', '주포']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15530</v>
+        <v>15500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.48%</t>
+          <t>'-3.67%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F11" t="n">
         <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H11" t="n">
         <v>9.630000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>43617073715</v>
+        <v>44680062635</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,18 +1487,18 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17330</v>
+        <v>17300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.78%</t>
+          <t>'-3.94%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F12" t="n">
         <v>50</v>
@@ -1530,7 +1530,7 @@
         <v>27.61</v>
       </c>
       <c r="O12" t="n">
-        <v>45890874880</v>
+        <v>47048280450</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6530</v>
+        <v>68100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.11%</t>
+          <t>'-4.76%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.3</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
+        <v>217</v>
+      </c>
+      <c r="F13" t="n">
         <v>145</v>
       </c>
-      <c r="F13" t="n">
-        <v>79</v>
-      </c>
       <c r="G13" t="n">
-        <v>566</v>
+        <v>668</v>
       </c>
       <c r="H13" t="n">
-        <v>12.27</v>
+        <v>22.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6810</v>
+        <v>71500</v>
       </c>
       <c r="K13" t="n">
-        <v>7150</v>
+        <v>68400</v>
       </c>
       <c r="L13" t="n">
-        <v>7160</v>
+        <v>70600</v>
       </c>
       <c r="M13" t="n">
-        <v>6440</v>
+        <v>67300</v>
       </c>
       <c r="N13" t="n">
-        <v>12.57</v>
+        <v>22.21</v>
       </c>
       <c r="O13" t="n">
-        <v>18527694935</v>
+        <v>120247712350</v>
       </c>
       <c r="P13" t="n">
-        <v>8850</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>4220</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>-606000</v>
+        <v>225000</v>
       </c>
       <c r="S13" t="n">
-        <v>-8000</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>의도적인 주가 누르기와 공매도에 대한 불만, 광주 송정역 부지 관련 기대감.</t>
+          <t>정치적 발언 및 개인적인 비난 위주의 게시글로, 객관적인 분석 근거 부재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '부지']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68200</v>
+        <v>6480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.62%</t>
+          <t>'-4.85%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.11</v>
+        <v>-0.3</v>
       </c>
       <c r="E14" t="n">
-        <v>215</v>
+        <v>143</v>
       </c>
       <c r="F14" t="n">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="G14" t="n">
-        <v>659</v>
+        <v>565</v>
       </c>
       <c r="H14" t="n">
-        <v>22.1</v>
+        <v>12.27</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>71500</v>
+        <v>6810</v>
       </c>
       <c r="K14" t="n">
-        <v>68400</v>
+        <v>7150</v>
       </c>
       <c r="L14" t="n">
-        <v>70600</v>
+        <v>7160</v>
       </c>
       <c r="M14" t="n">
-        <v>67300</v>
+        <v>6440</v>
       </c>
       <c r="N14" t="n">
-        <v>22.21</v>
+        <v>12.57</v>
       </c>
       <c r="O14" t="n">
-        <v>117626614950</v>
+        <v>18656632805</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>8850</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>4220</v>
       </c>
       <c r="R14" t="n">
-        <v>225000</v>
+        <v>-606000</v>
       </c>
       <c r="S14" t="n">
-        <v>2000</v>
+        <v>-8000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 요인 및 시장 상황으로 인한 주가 하락에 대한 불만, 정부 정책 비판.</t>
+          <t>의도적인 주가 누르기와 공매도에 대한 불만, 광주 송정역 부지 관련 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['공매도', '부지']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7340</v>
+        <v>7360</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.41%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.36</v>
       </c>
       <c r="E15" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H15" t="n">
         <v>26.01</v>
@@ -1806,7 +1806,7 @@
         <v>26.37</v>
       </c>
       <c r="O15" t="n">
-        <v>18933118465</v>
+        <v>19289555800</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1869,10 +1869,10 @@
         <v>116</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H16" t="n">
         <v>1.8</v>
@@ -1898,7 +1898,7 @@
         <v>1.99</v>
       </c>
       <c r="O16" t="n">
-        <v>62542587100</v>
+        <v>62763723455</v>
       </c>
       <c r="P16" t="n">
         <v>23500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>건설 기초 소재 관련 언급과 함께 매집 흔적 관찰 및 주가 지지 기대. 공매도 경계.</t>
+          <t>성수 메가프로젝트 및 건설기초소재 관련 언급, 바닥 지지 및 매집 물량 확인, 외국인 매수세.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['건설', '소재', '매집']</t>
+          <t>['성수메가프로젝트', '건설기초소재', '외국인']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,171 +1943,171 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>171600</v>
+        <v>14430</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-8.14%</t>
+          <t>'-8.21%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="G17" t="n">
-        <v>101</v>
+        <v>353</v>
       </c>
       <c r="H17" t="n">
-        <v>75.20999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>186800</v>
+        <v>15720</v>
       </c>
       <c r="K17" t="n">
-        <v>180800</v>
+        <v>14770</v>
       </c>
       <c r="L17" t="n">
-        <v>183000</v>
+        <v>15130</v>
       </c>
       <c r="M17" t="n">
-        <v>170500</v>
+        <v>14160</v>
       </c>
       <c r="N17" t="n">
-        <v>75.23</v>
+        <v>3.37</v>
       </c>
       <c r="O17" t="n">
-        <v>471317044450</v>
+        <v>67871425485</v>
       </c>
       <c r="P17" t="n">
-        <v>243500</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>70400</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-173000</v>
+        <v>85000</v>
       </c>
       <c r="S17" t="n">
-        <v>65000</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
+          <t>3분기 어닝 서프라이즈 기록, 외인 대량 매수 및 기술력 논란. 추세 하락 및 바닥 7000원 예상.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가하락', '시장붕괴', '외인매수']</t>
+          <t>['어닝서프라이즈', '광케이블', '외인매수']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14440</v>
+        <v>228500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.14%</t>
+          <t>'-8.78%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E18" t="n">
-        <v>106</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>67</v>
+        <v>576</v>
       </c>
       <c r="G18" t="n">
-        <v>349</v>
+        <v>2060</v>
       </c>
       <c r="H18" t="n">
-        <v>3.43</v>
+        <v>46.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>15720</v>
+        <v>250500</v>
       </c>
       <c r="K18" t="n">
-        <v>14770</v>
+        <v>241500</v>
       </c>
       <c r="L18" t="n">
-        <v>15130</v>
+        <v>244000</v>
       </c>
       <c r="M18" t="n">
-        <v>14160</v>
+        <v>228000</v>
       </c>
       <c r="N18" t="n">
-        <v>3.37</v>
+        <v>46.35</v>
       </c>
       <c r="O18" t="n">
-        <v>66795594410</v>
+        <v>3159666314500</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>90200</v>
       </c>
       <c r="R18" t="n">
-        <v>85000</v>
+        <v>-2204000</v>
       </c>
       <c r="S18" t="n">
-        <v>2000</v>
+        <v>241000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 및 외인 대량 매수 확인. 광케이블 기술력 논쟁 및 추세 하락 우려.</t>
+          <t>정치적 불만 및 정부 정책 비판, 금융시장 망가뜨린다는 주장.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '외인 매수', '광케이블']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>229000</v>
+        <v>170100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-8.58%</t>
+          <t>'-8.94%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>580</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>1951</v>
+        <v>103</v>
       </c>
       <c r="H19" t="n">
-        <v>46.3</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>250500</v>
+        <v>186800</v>
       </c>
       <c r="K19" t="n">
-        <v>241500</v>
+        <v>180800</v>
       </c>
       <c r="L19" t="n">
-        <v>244000</v>
+        <v>183000</v>
       </c>
       <c r="M19" t="n">
-        <v>228000</v>
+        <v>170000</v>
       </c>
       <c r="N19" t="n">
-        <v>46.35</v>
+        <v>75.23</v>
       </c>
       <c r="O19" t="n">
-        <v>3086155568250</v>
+        <v>490669915000</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>243500</v>
       </c>
       <c r="Q19" t="n">
-        <v>90200</v>
+        <v>70400</v>
       </c>
       <c r="R19" t="n">
-        <v>-2204000</v>
+        <v>-173000</v>
       </c>
       <c r="S19" t="n">
-        <v>241000</v>
+        <v>65000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>정부 정책 및 정치 성향에 따른 시장 불안감과 부정적 전망.</t>
+          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,20 +2199,20 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['정부', '시장', '정치']</t>
+          <t>['주가하락', '시장붕괴', '외인매수']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1460000</v>
+        <v>1450000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.03%</t>
+          <t>'-9.66%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G20" t="n">
-        <v>1702</v>
+        <v>1681</v>
       </c>
       <c r="H20" t="n">
         <v>49.41</v>
@@ -2260,13 +2260,13 @@
         <v>1554000</v>
       </c>
       <c r="M20" t="n">
-        <v>1449000</v>
+        <v>1447000</v>
       </c>
       <c r="N20" t="n">
         <v>49.52</v>
       </c>
       <c r="O20" t="n">
-        <v>4018591789000</v>
+        <v>4124577421500</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정치 및 경제 정책에 대한 불만과 주가 하락에 대한 부정적 의견.</t>
+          <t>정치권 및 특정 인물에 대한 강한 비난, 주가 하락 원인 지목.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['정치', '경제', '주가']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20261013_12.xlsx
+++ b/data/trending_integrated_20261013_12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87201472050</v>
+        <v>87286743410</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체 투자 및 경제자유구역 확대 수혜 기대, 연속 상한가 및 10연상 랠리 전망.</t>
+          <t>서산, 호남 반도체 관련 수혜주로 부각되며 급등 전망. 투자 주의 종목 지정 가능성에도 연상 랠리 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남반도체', '경제자유구역', '10연상']</t>
+          <t>['호남 반도체', '경제자유구역', '연상 랠리']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18380</v>
+        <v>4210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.42%</t>
+          <t>'+13.48%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.25</v>
+        <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16350</v>
+        <v>3710</v>
       </c>
       <c r="K3" t="n">
-        <v>15790</v>
+        <v>3555</v>
       </c>
       <c r="L3" t="n">
-        <v>19930</v>
+        <v>4440</v>
       </c>
       <c r="M3" t="n">
-        <v>15520</v>
+        <v>3475</v>
       </c>
       <c r="N3" t="n">
-        <v>1.13</v>
+        <v>0.78</v>
       </c>
       <c r="O3" t="n">
-        <v>219658329635</v>
+        <v>73440067279</v>
       </c>
       <c r="P3" t="n">
-        <v>19930</v>
+        <v>6660</v>
       </c>
       <c r="Q3" t="n">
-        <v>6320</v>
+        <v>2200</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-34000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>보안 기술 및 AI 관련 언급, 신고가 돌파 및 상승 기대감. 프랑스 국채 불안 언급.</t>
+          <t>녹십자엠에스, 페스트 및 독감 관련 이슈로 인한 주가 상승 기대감. 대세 상승 시작 및 변종 바이러스 우려.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '신고가']</t>
+          <t>['페스트', '독감', '대세 상승']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12290</v>
+        <v>18400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.02%</t>
+          <t>'+12.54%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.92</v>
+        <v>-0.25</v>
       </c>
       <c r="E4" t="n">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="F4" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G4" t="n">
-        <v>284</v>
+        <v>137</v>
       </c>
       <c r="H4" t="n">
-        <v>15.64</v>
+        <v>0.88</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11070</v>
+        <v>16350</v>
       </c>
       <c r="K4" t="n">
-        <v>11670</v>
+        <v>15790</v>
       </c>
       <c r="L4" t="n">
-        <v>13970</v>
+        <v>19930</v>
       </c>
       <c r="M4" t="n">
-        <v>11200</v>
+        <v>15520</v>
       </c>
       <c r="N4" t="n">
-        <v>14.72</v>
+        <v>1.13</v>
       </c>
       <c r="O4" t="n">
-        <v>300212331590</v>
+        <v>220784551295</v>
       </c>
       <c r="P4" t="n">
-        <v>14350</v>
+        <v>19930</v>
       </c>
       <c r="Q4" t="n">
-        <v>465</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-176000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주가 급등 및 물량 소화 중, 호남 클러스터 외 테마 죽음. "인생역전 주식" 기대감.</t>
+          <t>라온시큐어, 보안 기술 중요성 부각 및 52주 신고가 돌파 기대. AI 해킹 및 전 세계 불황 우려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남클러스터', '물갈이', '주포']</t>
+          <t>['보안주', '52주 신고가', 'AI 해킹']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1599</v>
+        <v>11920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.33%</t>
+          <t>'+7.68%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>160</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>192</v>
+        <v>289</v>
       </c>
       <c r="H5" t="n">
-        <v>0.32</v>
+        <v>15.64</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1578</v>
+        <v>11070</v>
       </c>
       <c r="K5" t="n">
-        <v>1578</v>
+        <v>11670</v>
       </c>
       <c r="L5" t="n">
-        <v>1776</v>
+        <v>13970</v>
       </c>
       <c r="M5" t="n">
-        <v>1457</v>
+        <v>11200</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>14.72</v>
       </c>
       <c r="O5" t="n">
-        <v>8422909799</v>
+        <v>302707793875</v>
       </c>
       <c r="P5" t="n">
-        <v>2930</v>
+        <v>14350</v>
       </c>
       <c r="Q5" t="n">
-        <v>910</v>
+        <v>465</v>
       </c>
       <c r="R5" t="n">
-        <v>34000</v>
+        <v>-176000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
+          <t>금호전기, 투자자들의 긍정적 기대감 속 주가 상승 전망. 호남클러스터 외 테마 소멸 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['경제자유구역', '전국구', '수혜주']</t>
+          <t>['호남클러스터', '주포', '물갈이']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13220</v>
+        <v>1603</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.42%</t>
+          <t>'+1.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.09</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>161</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13410</v>
+        <v>1578</v>
       </c>
       <c r="K6" t="n">
-        <v>13260</v>
+        <v>1578</v>
       </c>
       <c r="L6" t="n">
-        <v>14580</v>
+        <v>1776</v>
       </c>
       <c r="M6" t="n">
-        <v>12920</v>
+        <v>1457</v>
       </c>
       <c r="N6" t="n">
-        <v>0.21</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>59349847410</v>
+        <v>8471504958</v>
       </c>
       <c r="P6" t="n">
-        <v>28700</v>
+        <v>2930</v>
       </c>
       <c r="Q6" t="n">
-        <v>11600</v>
+        <v>910</v>
       </c>
       <c r="R6" t="n">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 경계, 리보&amp;캄렐 간암 1차 승인 기대감. 통합 IR 데이 주목.</t>
+          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '리보', '캄렐']</t>
+          <t>['경제자유구역', '전국구', '수혜주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43550</v>
+        <v>18390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.91%</t>
+          <t>'-0.86%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.23</v>
+        <v>-0.42</v>
       </c>
       <c r="E7" t="n">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>621</v>
+        <v>89</v>
       </c>
       <c r="H7" t="n">
-        <v>13.1</v>
+        <v>0.46</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>44400</v>
+        <v>18550</v>
       </c>
       <c r="K7" t="n">
-        <v>43300</v>
+        <v>17550</v>
       </c>
       <c r="L7" t="n">
-        <v>44100</v>
+        <v>19580</v>
       </c>
       <c r="M7" t="n">
-        <v>42250</v>
+        <v>17010</v>
       </c>
       <c r="N7" t="n">
-        <v>13.33</v>
+        <v>0.88</v>
       </c>
       <c r="O7" t="n">
-        <v>22307099975</v>
+        <v>69591125260</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>45000</v>
+        <v>-65000</v>
       </c>
       <c r="S7" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 182건 토론 포착</t>
+          <t>해킹 관련 이슈에도 지수 및 보안주 흐름에 따라 변동성 예상. 기대감 속 투자자 간 의견 분분.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['해킹', '보안주', '폭락']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6080</v>
+        <v>6130</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.09%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F8" t="n">
         <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H8" t="n">
         <v>0.6899999999999999</v>
@@ -1162,7 +1162,7 @@
         <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>22028746825</v>
+        <v>22171096145</v>
       </c>
       <c r="P8" t="n">
         <v>11370</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18040</v>
+        <v>13180</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.75%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.42</v>
+        <v>0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>171</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>89</v>
+        <v>221</v>
       </c>
       <c r="H9" t="n">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18550</v>
+        <v>13410</v>
       </c>
       <c r="K9" t="n">
-        <v>17550</v>
+        <v>13260</v>
       </c>
       <c r="L9" t="n">
-        <v>19580</v>
+        <v>14580</v>
       </c>
       <c r="M9" t="n">
-        <v>17010</v>
+        <v>12920</v>
       </c>
       <c r="N9" t="n">
-        <v>0.88</v>
+        <v>0.21</v>
       </c>
       <c r="O9" t="n">
-        <v>68571756800</v>
+        <v>59896978805</v>
       </c>
       <c r="P9" t="n">
-        <v>30550</v>
+        <v>28700</v>
       </c>
       <c r="Q9" t="n">
-        <v>6100</v>
+        <v>11600</v>
       </c>
       <c r="R9" t="n">
-        <v>-65000</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>해킹 관련 이슈에도 지수 및 보안주 흐름에 따라 변동성 예상. 기대감 속 투자자 간 의견 분분.</t>
+          <t>매수세보다 매도세가 강하게 작용하며 주가 상승에 장애가 발생하고 있다는 분석이 있음. 장중 상승 후 장 막판 하락하는 패턴이 반복되며, 매도 의견이 제시됨.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', '폭락']</t>
+          <t>['매수세', '매도세', '장중하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12920</v>
+        <v>43300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.58%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.01</v>
+        <v>-0.23</v>
       </c>
       <c r="E10" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="F10" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="G10" t="n">
-        <v>309</v>
+        <v>625</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13400</v>
+        <v>44400</v>
       </c>
       <c r="K10" t="n">
-        <v>13750</v>
+        <v>43300</v>
       </c>
       <c r="L10" t="n">
-        <v>15390</v>
+        <v>44100</v>
       </c>
       <c r="M10" t="n">
-        <v>12380</v>
+        <v>42250</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>13.33</v>
       </c>
       <c r="O10" t="n">
-        <v>173047253770</v>
+        <v>22724741700</v>
       </c>
       <c r="P10" t="n">
-        <v>19380</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3200</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-76000</v>
+        <v>45000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>호남 반도체 투자 관련 언급, 주가 상승 기대감 및 주포 움직임 주시.</t>
+          <t>리보&amp;캄렐 간암 1차 승인 기대감 언급. 신한 창구를 통한 매도세 및 일부 악성 매물대 소화 필요성 제기. 통합 IR 데이 예정.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['호남반도체', '속도전', '주포']</t>
+          <t>['리보', '캄렐', 'IR데이']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15500</v>
+        <v>15460</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.67%</t>
+          <t>'-3.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F11" t="n">
         <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="H11" t="n">
         <v>9.630000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>44680062635</v>
+        <v>45479008535</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>증시 전반의 부진 속에서 주가 하락 우려 및 공매도 관련 언급.</t>
+          <t>대우건설, 주가 하락 및 건설주 전반의 부진에 대한 우려. 공매도 및 지수 불안정성에 대한 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['증시', '공매도', '하락']</t>
+          <t>['국장', '공매도', '건설주']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17300</v>
+        <v>17290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.94%</t>
+          <t>'-4.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H12" t="n">
         <v>27.69</v>
@@ -1530,7 +1530,7 @@
         <v>27.61</v>
       </c>
       <c r="O12" t="n">
-        <v>47048280450</v>
+        <v>47982391080</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시. 주주 환원 정책 및 공매도 금지 촉구.</t>
+          <t>삼성중공업, FLNG 매출 확대 전망 및 목표가 상향 제시. 주가 부양 정책 및 공매도 금지 요구.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['FLNG', '매출확대', '주주환원']</t>
+          <t>['FLNG', '삼성중공업', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68100</v>
+        <v>6490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.76%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.11</v>
+        <v>-0.3</v>
       </c>
       <c r="E13" t="n">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="F13" t="n">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="G13" t="n">
-        <v>668</v>
+        <v>569</v>
       </c>
       <c r="H13" t="n">
-        <v>22.1</v>
+        <v>12.27</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>71500</v>
+        <v>6810</v>
       </c>
       <c r="K13" t="n">
-        <v>68400</v>
+        <v>7150</v>
       </c>
       <c r="L13" t="n">
-        <v>70600</v>
+        <v>7160</v>
       </c>
       <c r="M13" t="n">
-        <v>67300</v>
+        <v>6440</v>
       </c>
       <c r="N13" t="n">
-        <v>22.21</v>
+        <v>12.57</v>
       </c>
       <c r="O13" t="n">
-        <v>120247712350</v>
+        <v>18887027095</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>8850</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>4220</v>
       </c>
       <c r="R13" t="n">
-        <v>225000</v>
+        <v>-606000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>-8000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 발언 및 개인적인 비난 위주의 게시글로, 객관적인 분석 근거 부재.</t>
+          <t>금호타이어, 의도적인 주가 누르기에 대한 불만 표출 및 실적 기반 주가 상승 기대. 공매도 문제 지적.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['공매도', '영업이익', '호남테마']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6480</v>
+        <v>12710</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.85%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.3</v>
+        <v>-1.01</v>
       </c>
       <c r="E14" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F14" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
-        <v>565</v>
+        <v>313</v>
       </c>
       <c r="H14" t="n">
-        <v>12.27</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6810</v>
+        <v>13400</v>
       </c>
       <c r="K14" t="n">
-        <v>7150</v>
+        <v>13750</v>
       </c>
       <c r="L14" t="n">
-        <v>7160</v>
+        <v>15390</v>
       </c>
       <c r="M14" t="n">
-        <v>6440</v>
+        <v>12380</v>
       </c>
       <c r="N14" t="n">
-        <v>12.57</v>
+        <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>18656632805</v>
+        <v>174250002815</v>
       </c>
       <c r="P14" t="n">
-        <v>8850</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>4220</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>-606000</v>
+        <v>-76000</v>
       </c>
       <c r="S14" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>의도적인 주가 누르기와 공매도에 대한 불만, 광주 송정역 부지 관련 기대감.</t>
+          <t>금호건설, 호남 반도체 투자 이슈와 함께 주가 상승 기대. 단기적 등락 및 테마주 위험성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '부지']</t>
+          <t>['호남 반도체', '속도전', '금건']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7360</v>
+        <v>7320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.15%</t>
+          <t>'-5.67%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.36</v>
       </c>
       <c r="E15" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="H15" t="n">
         <v>26.01</v>
@@ -1806,7 +1806,7 @@
         <v>26.37</v>
       </c>
       <c r="O15" t="n">
-        <v>19289555800</v>
+        <v>19946601835</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6960</v>
+        <v>6900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.07%</t>
+          <t>'-6.88%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.19</v>
       </c>
       <c r="E16" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="H16" t="n">
         <v>1.8</v>
@@ -1898,7 +1898,7 @@
         <v>1.99</v>
       </c>
       <c r="O16" t="n">
-        <v>62763723455</v>
+        <v>63190016035</v>
       </c>
       <c r="P16" t="n">
         <v>23500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>성수 메가프로젝트 및 건설기초소재 관련 언급, 바닥 지지 및 매집 물량 확인, 외국인 매수세.</t>
+          <t>건설기초소재대장주로 언급되며 수도권 거점 공장 보유. 일부 투자자는 차익 실현 매도를 하였으나, 바닥 지지 및 매집 정황을 근거로 매수 진입을 고려하는 의견도 있음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['성수메가프로젝트', '건설기초소재', '외국인']</t>
+          <t>['건설기초소재', '거점공장', '매집']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,83 +1943,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14430</v>
+        <v>71100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-8.21%</t>
+          <t>'-7.30%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="E17" t="n">
-        <v>109</v>
+        <v>221</v>
       </c>
       <c r="F17" t="n">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="G17" t="n">
-        <v>353</v>
+        <v>694</v>
       </c>
       <c r="H17" t="n">
-        <v>3.43</v>
+        <v>22.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>15720</v>
+        <v>76700</v>
       </c>
       <c r="K17" t="n">
-        <v>14770</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>15130</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>14160</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.37</v>
+        <v>22.21</v>
       </c>
       <c r="O17" t="n">
-        <v>67871425485</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>85000</v>
+        <v>225000</v>
       </c>
       <c r="S17" t="n">
         <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 기록, 외인 대량 매수 및 기술력 논란. 추세 하락 및 바닥 7000원 예상.</t>
+          <t>정치적 이슈와 연관된 부정적 언급 다수. 송기훈 관련 내용 및 원전 사업 관련 불확실성 제기. 기술적 반등 가능성은 있으나 전반적으로 하락 추세.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '광케이블', '외인매수']</t>
+          <t>['정치이슈', '원전사업', '기술적반등']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,86 +2028,86 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>228500</v>
+        <v>14420</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.78%</t>
+          <t>'-8.27%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>110</v>
       </c>
       <c r="F18" t="n">
-        <v>576</v>
+        <v>71</v>
       </c>
       <c r="G18" t="n">
-        <v>2060</v>
+        <v>362</v>
       </c>
       <c r="H18" t="n">
-        <v>46.3</v>
+        <v>3.43</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>250500</v>
+        <v>15720</v>
       </c>
       <c r="K18" t="n">
-        <v>241500</v>
+        <v>14770</v>
       </c>
       <c r="L18" t="n">
-        <v>244000</v>
+        <v>15130</v>
       </c>
       <c r="M18" t="n">
-        <v>228000</v>
+        <v>14160</v>
       </c>
       <c r="N18" t="n">
-        <v>46.35</v>
+        <v>3.37</v>
       </c>
       <c r="O18" t="n">
-        <v>3159666314500</v>
+        <v>68784700975</v>
       </c>
       <c r="P18" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>90200</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-2204000</v>
+        <v>85000</v>
       </c>
       <c r="S18" t="n">
-        <v>241000</v>
+        <v>2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정치적 불만 및 정부 정책 비판, 금융시장 망가뜨린다는 주장.</t>
+          <t>3분기 매출액 668억, 영업이익 59억으로 전분기 대비 어닝 서프라이즈 기록. 미국 업체 광케이블 기술력 하락 언급 및 AI 거품론 우려로 인한 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['어닝서프라이즈', '광케이블', 'AI거품론']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>170100</v>
+        <v>170200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-8.94%</t>
+          <t>'-8.89%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="H19" t="n">
         <v>75.20999999999999</v>
@@ -2174,7 +2174,7 @@
         <v>75.23</v>
       </c>
       <c r="O19" t="n">
-        <v>490669915000</v>
+        <v>504696014450</v>
       </c>
       <c r="P19" t="n">
         <v>243500</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1450000</v>
+        <v>1453000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.66%</t>
+          <t>'-9.47%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="G20" t="n">
-        <v>1681</v>
+        <v>1599</v>
       </c>
       <c r="H20" t="n">
         <v>49.41</v>
@@ -2260,13 +2260,13 @@
         <v>1554000</v>
       </c>
       <c r="M20" t="n">
-        <v>1447000</v>
+        <v>1445000</v>
       </c>
       <c r="N20" t="n">
         <v>49.52</v>
       </c>
       <c r="O20" t="n">
-        <v>4124577421500</v>
+        <v>4211048088500</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정치권 및 특정 인물에 대한 강한 비난, 주가 하락 원인 지목.</t>
+          <t>SK하이닉스, 정치적 이슈와 연계된 주가 하락 및 부정적 전망. 투자자들의 손실 및 불만 토로.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['민주당', '최태원', '주식시장']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2305,6 +2305,98 @@
       <c r="Z20" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>229000</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>'-12.93%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E21" t="n">
+        <v>800</v>
+      </c>
+      <c r="F21" t="n">
+        <v>578</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1923</v>
+      </c>
+      <c r="H21" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>263000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3230916000000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-2204000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>241000</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>삼성전자, 정치적 이슈와 정부 정책에 대한 부정적 의견 다수. 금융시장 불안감 및 투자 철회 의견.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['민주당', '이재명', '금융시장']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>005930</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261013_12.xlsx
+++ b/data/trending_integrated_20261013_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87286743410</v>
+        <v>87336490890</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>서산, 호남 반도체 관련 수혜주로 부각되며 급등 전망. 투자 주의 종목 지정 가능성에도 연상 랠리 기대.</t>
+          <t>무차입 경영, 10연상 기대감, 호남반도체 관련 수혜주 부각 등 강한 상승 기대감과 긍정적 뉴스 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남 반도체', '경제자유구역', '연상 랠리']</t>
+          <t>['무차입 경영', '호남반도체']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4210</v>
+        <v>18030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.48%</t>
+          <t>'+10.28%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.13</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3710</v>
+        <v>16350</v>
       </c>
       <c r="K3" t="n">
-        <v>3555</v>
+        <v>15790</v>
       </c>
       <c r="L3" t="n">
-        <v>4440</v>
+        <v>19930</v>
       </c>
       <c r="M3" t="n">
-        <v>3475</v>
+        <v>15520</v>
       </c>
       <c r="N3" t="n">
-        <v>0.78</v>
+        <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>73440067279</v>
+        <v>224812172645</v>
       </c>
       <c r="P3" t="n">
-        <v>6660</v>
+        <v>19930</v>
       </c>
       <c r="Q3" t="n">
-        <v>2200</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>-34000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>녹십자엠에스, 페스트 및 독감 관련 이슈로 인한 주가 상승 기대감. 대세 상승 시작 및 변종 바이러스 우려.</t>
+          <t>미국 보안주 폭락 속에서도 신고가 돌파 기대감, AI 해킹 관련 기술력 부각 등 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['페스트', '독감', '대세 상승']</t>
+          <t>['보안주', 'AI', '신고가']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18400</v>
+        <v>11910</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.54%</t>
+          <t>'+7.59%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.25</v>
+        <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="F4" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>137</v>
+        <v>292</v>
       </c>
       <c r="H4" t="n">
-        <v>0.88</v>
+        <v>15.64</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16350</v>
+        <v>11070</v>
       </c>
       <c r="K4" t="n">
-        <v>15790</v>
+        <v>11670</v>
       </c>
       <c r="L4" t="n">
-        <v>19930</v>
+        <v>13970</v>
       </c>
       <c r="M4" t="n">
-        <v>15520</v>
+        <v>11200</v>
       </c>
       <c r="N4" t="n">
-        <v>1.13</v>
+        <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>220784551295</v>
+        <v>308905726825</v>
       </c>
       <c r="P4" t="n">
-        <v>19930</v>
+        <v>14350</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>465</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-176000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>라온시큐어, 보안 기술 중요성 부각 및 52주 신고가 돌파 기대. AI 해킹 및 전 세계 불황 우려.</t>
+          <t>주가 급등 및 물량 소화 중, 호남 클러스터 외 테마 죽음. "인생역전 주식" 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안주', '52주 신고가', 'AI 해킹']</t>
+          <t>['호남클러스터', '물갈이', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11920</v>
+        <v>3880</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.68%</t>
+          <t>'+4.58%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.92</v>
+        <v>0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>289</v>
+        <v>126</v>
       </c>
       <c r="H5" t="n">
-        <v>15.64</v>
+        <v>0.91</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11070</v>
+        <v>3710</v>
       </c>
       <c r="K5" t="n">
-        <v>11670</v>
+        <v>3555</v>
       </c>
       <c r="L5" t="n">
-        <v>13970</v>
+        <v>4440</v>
       </c>
       <c r="M5" t="n">
-        <v>11200</v>
+        <v>3475</v>
       </c>
       <c r="N5" t="n">
-        <v>14.72</v>
+        <v>0.78</v>
       </c>
       <c r="O5" t="n">
-        <v>302707793875</v>
+        <v>78607091499</v>
       </c>
       <c r="P5" t="n">
-        <v>14350</v>
+        <v>6660</v>
       </c>
       <c r="Q5" t="n">
-        <v>465</v>
+        <v>2200</v>
       </c>
       <c r="R5" t="n">
-        <v>-176000</v>
+        <v>-34000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>금호전기, 투자자들의 긍정적 기대감 속 주가 상승 전망. 호남클러스터 외 테마 소멸 가능성 언급.</t>
+          <t>녹십자엠에스, 페스트 및 독감 관련 이슈로 인한 주가 상승 기대감. 대세 상승 시작 및 변종 바이러스 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['호남클러스터', '주포', '물갈이']</t>
+          <t>['페스트', '독감', '대세 상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.58%</t>
+          <t>'+1.52%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
         <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
         <v>0.32</v>
@@ -978,7 +978,7 @@
         <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>8471504958</v>
+        <v>8502501450</v>
       </c>
       <c r="P6" t="n">
         <v>2930</v>
@@ -987,7 +987,7 @@
         <v>910</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18390</v>
+        <v>13400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.86%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.42</v>
+        <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>86</v>
+        <v>176</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>89</v>
+        <v>229</v>
       </c>
       <c r="H7" t="n">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18550</v>
+        <v>13410</v>
       </c>
       <c r="K7" t="n">
-        <v>17550</v>
+        <v>13260</v>
       </c>
       <c r="L7" t="n">
-        <v>19580</v>
+        <v>14580</v>
       </c>
       <c r="M7" t="n">
-        <v>17010</v>
+        <v>12920</v>
       </c>
       <c r="N7" t="n">
-        <v>0.88</v>
+        <v>0.21</v>
       </c>
       <c r="O7" t="n">
-        <v>69591125260</v>
+        <v>60365038605</v>
       </c>
       <c r="P7" t="n">
-        <v>30550</v>
+        <v>28700</v>
       </c>
       <c r="Q7" t="n">
-        <v>6100</v>
+        <v>11600</v>
       </c>
       <c r="R7" t="n">
-        <v>-65000</v>
+        <v>34000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>해킹 관련 이슈에도 지수 및 보안주 흐름에 따라 변동성 예상. 기대감 속 투자자 간 의견 분분.</t>
+          <t>공매도 및 장난질에 대한 부정적 언급과 함께 일부 매수세 유입 가능성 언급, 전반적으로 혼조세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', '폭락']</t>
+          <t>['공매도', '매수세']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6130</v>
+        <v>18300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.29%</t>
+          <t>'-1.35%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.42</v>
       </c>
       <c r="E8" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6210</v>
+        <v>18550</v>
       </c>
       <c r="K8" t="n">
-        <v>5950</v>
+        <v>17550</v>
       </c>
       <c r="L8" t="n">
-        <v>6560</v>
+        <v>19580</v>
       </c>
       <c r="M8" t="n">
-        <v>5840</v>
+        <v>17010</v>
       </c>
       <c r="N8" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="O8" t="n">
-        <v>22171096145</v>
+        <v>70101990790</v>
       </c>
       <c r="P8" t="n">
-        <v>11370</v>
+        <v>30550</v>
       </c>
       <c r="Q8" t="n">
-        <v>3300</v>
+        <v>6100</v>
       </c>
       <c r="R8" t="n">
-        <v>-5000</v>
+        <v>-65000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>국내 해킹 비상 및 프랑스 매장 해킹 사례 언급, 보안주로서의 상승 기대감과 라온시큐어와의 비교 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['해킹', '보안주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,43 +1195,43 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13180</v>
+        <v>43400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-2.25%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.09</v>
+        <v>-0.23</v>
       </c>
       <c r="E9" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="F9" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="G9" t="n">
-        <v>221</v>
+        <v>631</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3</v>
+        <v>13.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13410</v>
+        <v>44400</v>
       </c>
       <c r="K9" t="n">
-        <v>13260</v>
+        <v>43300</v>
       </c>
       <c r="L9" t="n">
-        <v>14580</v>
+        <v>44100</v>
       </c>
       <c r="M9" t="n">
-        <v>12920</v>
+        <v>42250</v>
       </c>
       <c r="N9" t="n">
-        <v>0.21</v>
+        <v>13.33</v>
       </c>
       <c r="O9" t="n">
-        <v>59896978805</v>
+        <v>23378456525</v>
       </c>
       <c r="P9" t="n">
-        <v>28700</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>11600</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>매수세보다 매도세가 강하게 작용하며 주가 상승에 장애가 발생하고 있다는 분석이 있음. 장중 상승 후 장 막판 하락하는 패턴이 반복되며, 매도 의견이 제시됨.</t>
+          <t>리보&amp;캄렐 간암 1차 승인 기대감 언급. 신한 창구를 통한 매도세 및 일부 악성 매물대 소화 필요성 제기. 통합 IR 데이 예정.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['매수세', '매도세', '장중하락']</t>
+          <t>['리보', '캄렐', 'IR데이']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43300</v>
+        <v>6060</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.23</v>
+        <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>625</v>
+        <v>120</v>
       </c>
       <c r="H10" t="n">
-        <v>13.1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>44400</v>
+        <v>6210</v>
       </c>
       <c r="K10" t="n">
-        <v>43300</v>
+        <v>5950</v>
       </c>
       <c r="L10" t="n">
-        <v>44100</v>
+        <v>6560</v>
       </c>
       <c r="M10" t="n">
-        <v>42250</v>
+        <v>5840</v>
       </c>
       <c r="N10" t="n">
-        <v>13.33</v>
+        <v>0.75</v>
       </c>
       <c r="O10" t="n">
-        <v>22724741700</v>
+        <v>22356572225</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>11370</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>3300</v>
       </c>
       <c r="R10" t="n">
-        <v>45000</v>
+        <v>-5000</v>
       </c>
       <c r="S10" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>리보&amp;캄렐 간암 1차 승인 기대감 언급. 신한 창구를 통한 매도세 및 일부 악성 매물대 소화 필요성 제기. 통합 IR 데이 예정.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['리보', '캄렐', 'IR데이']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15460</v>
+        <v>15660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.92%</t>
+          <t>'-2.67%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F11" t="n">
         <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="H11" t="n">
         <v>9.630000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>45479008535</v>
+        <v>46945858665</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17290</v>
+        <v>17420</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.00%</t>
+          <t>'-3.28%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H12" t="n">
         <v>27.69</v>
@@ -1530,7 +1530,7 @@
         <v>27.61</v>
       </c>
       <c r="O12" t="n">
-        <v>47982391080</v>
+        <v>49133827685</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성중공업, FLNG 매출 확대 전망 및 목표가 상향 제시. 주가 부양 정책 및 공매도 금지 요구.</t>
+          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시, 공매도 금지 요구 등 긍정적 전망과 부정적 시장 상황 언급이 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['FLNG', '삼성중공업', '공매도']</t>
+          <t>['FLNG', '목표가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6490</v>
+        <v>68600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.70%</t>
+          <t>'-4.06%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.3</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
+        <v>221</v>
+      </c>
+      <c r="F13" t="n">
         <v>146</v>
       </c>
-      <c r="F13" t="n">
-        <v>79</v>
-      </c>
       <c r="G13" t="n">
-        <v>569</v>
+        <v>707</v>
       </c>
       <c r="H13" t="n">
-        <v>12.27</v>
+        <v>22.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6810</v>
+        <v>71500</v>
       </c>
       <c r="K13" t="n">
-        <v>7150</v>
+        <v>68400</v>
       </c>
       <c r="L13" t="n">
-        <v>7160</v>
+        <v>70600</v>
       </c>
       <c r="M13" t="n">
-        <v>6440</v>
+        <v>67300</v>
       </c>
       <c r="N13" t="n">
-        <v>12.57</v>
+        <v>22.21</v>
       </c>
       <c r="O13" t="n">
-        <v>18887027095</v>
+        <v>128624573650</v>
       </c>
       <c r="P13" t="n">
-        <v>8850</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>4220</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>-606000</v>
+        <v>225000</v>
       </c>
       <c r="S13" t="n">
-        <v>-8000</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>금호타이어, 의도적인 주가 누르기에 대한 불만 표출 및 실적 기반 주가 상승 기대. 공매도 문제 지적.</t>
+          <t>정치적 이슈와 연관된 부정적 언급 다수. 송기훈 관련 내용 및 원전 사업 관련 불확실성 제기. 기술적 반등 가능성은 있으나 전반적으로 하락 추세.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '영업이익', '호남테마']</t>
+          <t>['정치이슈', '원전사업', '기술적반등']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12710</v>
+        <v>6520</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.15%</t>
+          <t>'-4.26%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.01</v>
+        <v>-0.3</v>
       </c>
       <c r="E14" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G14" t="n">
-        <v>313</v>
+        <v>580</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>12.27</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13400</v>
+        <v>6810</v>
       </c>
       <c r="K14" t="n">
-        <v>13750</v>
+        <v>7150</v>
       </c>
       <c r="L14" t="n">
-        <v>15390</v>
+        <v>7160</v>
       </c>
       <c r="M14" t="n">
-        <v>12380</v>
+        <v>6440</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>12.57</v>
       </c>
       <c r="O14" t="n">
-        <v>174250002815</v>
+        <v>19041046565</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>8850</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>4220</v>
       </c>
       <c r="R14" t="n">
-        <v>-76000</v>
+        <v>-606000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 투자 이슈와 함께 주가 상승 기대. 단기적 등락 및 테마주 위험성 언급.</t>
+          <t>금호타이어, 의도적인 주가 누르기에 대한 불만 표출 및 실적 기반 주가 상승 기대. 공매도 문제 지적.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['호남 반도체', '속도전', '금건']</t>
+          <t>['공매도', '영업이익', '호남테마']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7320</v>
+        <v>7380</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.67%</t>
+          <t>'-4.90%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.36</v>
       </c>
       <c r="E15" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G15" t="n">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="H15" t="n">
         <v>26.01</v>
@@ -1806,7 +1806,7 @@
         <v>26.37</v>
       </c>
       <c r="O15" t="n">
-        <v>19946601835</v>
+        <v>20388574940</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락 및 실적 악화에 대한 우려, 회사 경영진 비판.</t>
+          <t>주가 하락에 대한 부정적 언급과 함께 FLiPP 투자 시작, 증착기 구매 등 일부 긍정적 기술 투자 내용 포함.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가', '실적', '경영진']</t>
+          <t>['FLiPP', '증착기']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6900</v>
+        <v>12680</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.88%</t>
+          <t>'-5.37%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.19</v>
+        <v>-1.01</v>
       </c>
       <c r="E16" t="n">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G16" t="n">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7410</v>
+        <v>13400</v>
       </c>
       <c r="K16" t="n">
-        <v>7330</v>
+        <v>13750</v>
       </c>
       <c r="L16" t="n">
-        <v>8040</v>
+        <v>15390</v>
       </c>
       <c r="M16" t="n">
-        <v>6890</v>
+        <v>12380</v>
       </c>
       <c r="N16" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
-        <v>63190016035</v>
+        <v>176466802570</v>
       </c>
       <c r="P16" t="n">
-        <v>23500</v>
+        <v>19380</v>
       </c>
       <c r="Q16" t="n">
-        <v>2890</v>
+        <v>3200</v>
       </c>
       <c r="R16" t="n">
-        <v>-241000</v>
+        <v>-76000</v>
       </c>
       <c r="S16" t="n">
-        <v>-130000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>건설기초소재대장주로 언급되며 수도권 거점 공장 보유. 일부 투자자는 차익 실현 매도를 하였으나, 바닥 지지 및 매집 정황을 근거로 매수 진입을 고려하는 의견도 있음.</t>
+          <t>금호건설, 호남 반도체 투자 이슈와 함께 주가 상승 기대. 단기적 등락 및 테마주 위험성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['건설기초소재', '거점공장', '매집']</t>
+          <t>['호남 반도체', '속도전', '금건']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>71100</v>
+        <v>6870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.30%</t>
+          <t>'-7.29%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="E17" t="n">
-        <v>221</v>
+        <v>119</v>
       </c>
       <c r="F17" t="n">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>694</v>
+        <v>314</v>
       </c>
       <c r="H17" t="n">
-        <v>22.1</v>
+        <v>1.8</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>76700</v>
+        <v>7410</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>7330</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>8040</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6850</v>
       </c>
       <c r="N17" t="n">
-        <v>22.21</v>
+        <v>1.99</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>63866344820</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>23500</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2890</v>
       </c>
       <c r="R17" t="n">
-        <v>225000</v>
+        <v>-241000</v>
       </c>
       <c r="S17" t="n">
-        <v>2000</v>
+        <v>-130000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 부정적 언급 다수. 송기훈 관련 내용 및 원전 사업 관련 불확실성 제기. 기술적 반등 가능성은 있으나 전반적으로 하락 추세.</t>
+          <t>건설기초소재대장주로 언급되며 수도권 거점 공장 보유. 일부 투자자는 차익 실현 매도를 하였으나, 바닥 지지 및 매집 정황을 근거로 매수 진입을 고려하는 의견도 있음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['정치이슈', '원전사업', '기술적반등']</t>
+          <t>['건설기초소재', '거점공장', '매집']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14420</v>
+        <v>14570</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.27%</t>
+          <t>'-7.32%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F18" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G18" t="n">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H18" t="n">
         <v>3.43</v>
@@ -2082,7 +2082,7 @@
         <v>3.37</v>
       </c>
       <c r="O18" t="n">
-        <v>68784700975</v>
+        <v>70050514900</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>170200</v>
+        <v>172800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-8.89%</t>
+          <t>'-7.49%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H19" t="n">
         <v>75.20999999999999</v>
@@ -2174,7 +2174,7 @@
         <v>75.23</v>
       </c>
       <c r="O19" t="n">
-        <v>504696014450</v>
+        <v>522643062750</v>
       </c>
       <c r="P19" t="n">
         <v>243500</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1453000</v>
+        <v>1468000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.47%</t>
+          <t>'-8.54%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G20" t="n">
-        <v>1599</v>
+        <v>1652</v>
       </c>
       <c r="H20" t="n">
         <v>49.41</v>
@@ -2266,7 +2266,7 @@
         <v>49.52</v>
       </c>
       <c r="O20" t="n">
-        <v>4211048088500</v>
+        <v>4351175384500</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>SK하이닉스, 정치적 이슈와 연계된 주가 하락 및 부정적 전망. 투자자들의 손실 및 불만 토로.</t>
+          <t>정치적 논쟁과 특정 인물에 대한 비난이 주를 이루며, 주식 시장 상황에 대한 부정적 인식이 나타남.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['민주당', '최태원', '주식시장']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>229000</v>
+        <v>231500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-12.93%</t>
+          <t>'-11.98%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G21" t="n">
-        <v>1923</v>
+        <v>1849</v>
       </c>
       <c r="H21" t="n">
         <v>46.3</v>
@@ -2358,7 +2358,7 @@
         <v>46.35</v>
       </c>
       <c r="O21" t="n">
-        <v>3230916000000</v>
+        <v>3312827000000</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>삼성전자, 정치적 이슈와 정부 정책에 대한 부정적 의견 다수. 금융시장 불안감 및 투자 철회 의견.</t>
+          <t>정치적 비난과 지역 감정 조장이 주를 이루며, 특정 정치인에 대한 부정적 언급이 다수 포함됨.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['민주당', '이재명', '금융시장']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X21" t="n">

--- a/data/trending_integrated_20261013_12.xlsx
+++ b/data/trending_integrated_20261013_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G2" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87336490890</v>
+        <v>87378380270</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>무차입 경영, 10연상 기대감, 호남반도체 관련 수혜주 부각 등 강한 상승 기대감과 긍정적 뉴스 언급.</t>
+          <t>독보적인 상승 추세 및 10년간 움직이지 않던 자리 돌파, 광주 경제자유구역 확대 수혜 기대감 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['무차입 경영', '호남반도체']</t>
+          <t>['텐버거', '경제자유구역', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,18 +659,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18030</v>
+        <v>17700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.28%</t>
+          <t>'+8.26%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F3" t="n">
         <v>85</v>
@@ -702,7 +702,7 @@
         <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>224812172645</v>
+        <v>228819553470</v>
       </c>
       <c r="P3" t="n">
         <v>19930</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11910</v>
+        <v>3965</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.59%</t>
+          <t>'+6.87%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.92</v>
+        <v>0.13</v>
       </c>
       <c r="E4" t="n">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>292</v>
+        <v>126</v>
       </c>
       <c r="H4" t="n">
-        <v>15.64</v>
+        <v>0.91</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11070</v>
+        <v>3710</v>
       </c>
       <c r="K4" t="n">
-        <v>11670</v>
+        <v>3555</v>
       </c>
       <c r="L4" t="n">
-        <v>13970</v>
+        <v>4440</v>
       </c>
       <c r="M4" t="n">
-        <v>11200</v>
+        <v>3475</v>
       </c>
       <c r="N4" t="n">
-        <v>14.72</v>
+        <v>0.78</v>
       </c>
       <c r="O4" t="n">
-        <v>308905726825</v>
+        <v>81820876305</v>
       </c>
       <c r="P4" t="n">
-        <v>14350</v>
+        <v>6660</v>
       </c>
       <c r="Q4" t="n">
-        <v>465</v>
+        <v>2200</v>
       </c>
       <c r="R4" t="n">
-        <v>-176000</v>
+        <v>-34000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주가 급등 및 물량 소화 중, 호남 클러스터 외 테마 죽음. "인생역전 주식" 기대감.</t>
+          <t>녹십자엠에스, 페스트 및 독감 관련 이슈로 인한 주가 상승 기대감. 대세 상승 시작 및 변종 바이러스 우려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남클러스터', '물갈이', '주포']</t>
+          <t>['페스트', '독감', '대세 상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3880</v>
+        <v>11580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.58%</t>
+          <t>'+4.61%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.13</v>
+        <v>0.92</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="F5" t="n">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="G5" t="n">
-        <v>126</v>
+        <v>331</v>
       </c>
       <c r="H5" t="n">
-        <v>0.91</v>
+        <v>15.64</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3710</v>
+        <v>11070</v>
       </c>
       <c r="K5" t="n">
-        <v>3555</v>
+        <v>11670</v>
       </c>
       <c r="L5" t="n">
-        <v>4440</v>
+        <v>13970</v>
       </c>
       <c r="M5" t="n">
-        <v>3475</v>
+        <v>11200</v>
       </c>
       <c r="N5" t="n">
-        <v>0.78</v>
+        <v>14.72</v>
       </c>
       <c r="O5" t="n">
-        <v>78607091499</v>
+        <v>313940152890</v>
       </c>
       <c r="P5" t="n">
-        <v>6660</v>
+        <v>14350</v>
       </c>
       <c r="Q5" t="n">
-        <v>2200</v>
+        <v>465</v>
       </c>
       <c r="R5" t="n">
-        <v>-34000</v>
+        <v>-176000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>녹십자엠에스, 페스트 및 독감 관련 이슈로 인한 주가 상승 기대감. 대세 상승 시작 및 변종 바이러스 우려.</t>
+          <t>호남클러스터 외 테마 사망 및 물갈이론 언급, 주가 급등 기대와 계단식 하락 경고 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['페스트', '독감', '대세 상승']</t>
+          <t>['주포', '물갈이', '계단식 하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1602</v>
+        <v>13410</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.52%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="G6" t="n">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,28 +963,28 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1578</v>
+        <v>13410</v>
       </c>
       <c r="K6" t="n">
-        <v>1578</v>
+        <v>13260</v>
       </c>
       <c r="L6" t="n">
-        <v>1776</v>
+        <v>14580</v>
       </c>
       <c r="M6" t="n">
-        <v>1457</v>
+        <v>12920</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>0.21</v>
       </c>
       <c r="O6" t="n">
-        <v>8502501450</v>
+        <v>61543567335</v>
       </c>
       <c r="P6" t="n">
-        <v>2930</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>910</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
         <v>34000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
+          <t>주가 하락에 대한 좌절감과 함께 매수세 대비 매도세 우위, 종가 하락 예상 등 부정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,51 +1003,51 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['경제자유구역', '전국구', '수혜주']</t>
+          <t>['매도세', '주가 하락', '종가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13400</v>
+        <v>1568</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'-0.63%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.09</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13410</v>
+        <v>1578</v>
       </c>
       <c r="K7" t="n">
-        <v>13260</v>
+        <v>1578</v>
       </c>
       <c r="L7" t="n">
-        <v>14580</v>
+        <v>1776</v>
       </c>
       <c r="M7" t="n">
-        <v>12920</v>
+        <v>1457</v>
       </c>
       <c r="N7" t="n">
-        <v>0.21</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
-        <v>60365038605</v>
+        <v>8594601303</v>
       </c>
       <c r="P7" t="n">
-        <v>28700</v>
+        <v>2930</v>
       </c>
       <c r="Q7" t="n">
-        <v>11600</v>
+        <v>910</v>
       </c>
       <c r="R7" t="n">
         <v>34000</v>
@@ -1086,29 +1086,29 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>공매도 및 장난질에 대한 부정적 언급과 함께 일부 매수세 유입 가능성 언급, 전반적으로 혼조세.</t>
+          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도', '매수세']</t>
+          <t>['경제자유구역', '전국구', '수혜주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1119,18 +1119,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18300</v>
+        <v>18150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.35%</t>
+          <t>'-2.16%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.42</v>
       </c>
       <c r="E8" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
         <v>40</v>
@@ -1162,7 +1162,7 @@
         <v>0.88</v>
       </c>
       <c r="O8" t="n">
-        <v>70101990790</v>
+        <v>70451567840</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43400</v>
+        <v>43250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.25%</t>
+          <t>'-2.59%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.23</v>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F9" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G9" t="n">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="H9" t="n">
         <v>13.1</v>
@@ -1254,7 +1254,7 @@
         <v>13.33</v>
       </c>
       <c r="O9" t="n">
-        <v>23378456525</v>
+        <v>23670145475</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>리보&amp;캄렐 간암 1차 승인 기대감 언급. 신한 창구를 통한 매도세 및 일부 악성 매물대 소화 필요성 제기. 통합 IR 데이 예정.</t>
+          <t>공매도 세력에 대한 경계와 함께 간암 1차 승인 기대감, 악성 매물 소화 필요성 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['리보', '캄렐', 'IR데이']</t>
+          <t>['공매도', '간암 1차', '악성 매물']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,123 +1299,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6060</v>
+        <v>15630</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.42%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
-        <v>120</v>
+        <v>344</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6210</v>
+        <v>16090</v>
       </c>
       <c r="K10" t="n">
-        <v>5950</v>
+        <v>15190</v>
       </c>
       <c r="L10" t="n">
-        <v>6560</v>
+        <v>15980</v>
       </c>
       <c r="M10" t="n">
-        <v>5840</v>
+        <v>15100</v>
       </c>
       <c r="N10" t="n">
-        <v>0.75</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>22356572225</v>
+        <v>47668300015</v>
       </c>
       <c r="P10" t="n">
-        <v>11370</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>3300</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-5000</v>
+        <v>395000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>장 상황 악화 및 도배글에 대한 불만, 금감원 사모펀드 긴급 점검 언급과 함께 주가 하락 우려 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['국장', '도배글', '금감원']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15660</v>
+        <v>17430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.67%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>327</v>
+        <v>286</v>
       </c>
       <c r="H11" t="n">
-        <v>9.630000000000001</v>
+        <v>27.69</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16090</v>
+        <v>18010</v>
       </c>
       <c r="K11" t="n">
-        <v>15190</v>
+        <v>17430</v>
       </c>
       <c r="L11" t="n">
-        <v>15980</v>
+        <v>17840</v>
       </c>
       <c r="M11" t="n">
-        <v>15100</v>
+        <v>17210</v>
       </c>
       <c r="N11" t="n">
-        <v>9.470000000000001</v>
+        <v>27.61</v>
       </c>
       <c r="O11" t="n">
-        <v>46945858665</v>
+        <v>49849103730</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>17210</v>
       </c>
       <c r="R11" t="n">
-        <v>395000</v>
+        <v>681000</v>
       </c>
       <c r="S11" t="n">
-        <v>31000</v>
+        <v>71000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대우건설, 주가 하락 및 건설주 전반의 부진에 대한 우려. 공매도 및 지수 불안정성에 대한 언급.</t>
+          <t>FLNG 매출 확대 전망 뉴스 인용 및 목표가 42,000원 언급, 주주 환원 정책 요구 및 현 주가 불만 표출.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['국장', '공매도', '건설주']</t>
+          <t>['FLNG', '매출 전망', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,99 +1476,99 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17420</v>
+        <v>5990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.28%</t>
+          <t>'-3.54%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>268</v>
+        <v>119</v>
       </c>
       <c r="H12" t="n">
-        <v>27.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18010</v>
+        <v>6210</v>
       </c>
       <c r="K12" t="n">
-        <v>17430</v>
+        <v>5950</v>
       </c>
       <c r="L12" t="n">
-        <v>17840</v>
+        <v>6560</v>
       </c>
       <c r="M12" t="n">
-        <v>17210</v>
+        <v>5840</v>
       </c>
       <c r="N12" t="n">
-        <v>27.61</v>
+        <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>49133827685</v>
+        <v>22547017915</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>11370</v>
       </c>
       <c r="Q12" t="n">
-        <v>17210</v>
+        <v>3300</v>
       </c>
       <c r="R12" t="n">
-        <v>681000</v>
+        <v>-5000</v>
       </c>
       <c r="S12" t="n">
-        <v>71000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시, 공매도 금지 요구 등 긍정적 전망과 부정적 시장 상황 언급이 혼재.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['FLNG', '목표가']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -1590,13 +1590,13 @@
         <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F13" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G13" t="n">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="H13" t="n">
         <v>22.1</v>
@@ -1622,7 +1622,7 @@
         <v>22.21</v>
       </c>
       <c r="O13" t="n">
-        <v>128624573650</v>
+        <v>130388161500</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 부정적 언급 다수. 송기훈 관련 내용 및 원전 사업 관련 불확실성 제기. 기술적 반등 가능성은 있으나 전반적으로 하락 추세.</t>
+          <t>주가 부양 실패 및 도박판 비유, 특정 정치인 비난과 함께 반대매매 및 주가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치이슈', '원전사업', '기술적반등']</t>
+          <t>['도박판', '반대매매', '주가 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6520</v>
+        <v>7410</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.26%</t>
+          <t>'-4.51%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.3</v>
+        <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="F14" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="G14" t="n">
-        <v>580</v>
+        <v>404</v>
       </c>
       <c r="H14" t="n">
-        <v>12.27</v>
+        <v>26.01</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6810</v>
+        <v>7760</v>
       </c>
       <c r="K14" t="n">
-        <v>7150</v>
+        <v>7650</v>
       </c>
       <c r="L14" t="n">
-        <v>7160</v>
+        <v>7680</v>
       </c>
       <c r="M14" t="n">
-        <v>6440</v>
+        <v>7300</v>
       </c>
       <c r="N14" t="n">
-        <v>12.57</v>
+        <v>26.37</v>
       </c>
       <c r="O14" t="n">
-        <v>19041046565</v>
+        <v>20849576465</v>
       </c>
       <c r="P14" t="n">
-        <v>8850</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>4220</v>
+        <v>7300</v>
       </c>
       <c r="R14" t="n">
-        <v>-606000</v>
+        <v>-510000</v>
       </c>
       <c r="S14" t="n">
-        <v>-8000</v>
+        <v>19000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>금호타이어, 의도적인 주가 누르기에 대한 불만 표출 및 실적 기반 주가 상승 기대. 공매도 문제 지적.</t>
+          <t>주가 하락에 대한 부정적 언급과 함께 FLiPP 투자 시작, 증착기 구매 등 일부 긍정적 기술 투자 내용 포함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '영업이익', '호남테마']</t>
+          <t>['FLiPP', '증착기']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7380</v>
+        <v>6500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.90%</t>
+          <t>'-4.55%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.36</v>
+        <v>-0.3</v>
       </c>
       <c r="E15" t="n">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="F15" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="G15" t="n">
-        <v>396</v>
+        <v>589</v>
       </c>
       <c r="H15" t="n">
-        <v>26.01</v>
+        <v>12.27</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7760</v>
+        <v>6810</v>
       </c>
       <c r="K15" t="n">
-        <v>7650</v>
+        <v>7150</v>
       </c>
       <c r="L15" t="n">
-        <v>7680</v>
+        <v>7160</v>
       </c>
       <c r="M15" t="n">
-        <v>7300</v>
+        <v>6440</v>
       </c>
       <c r="N15" t="n">
-        <v>26.37</v>
+        <v>12.57</v>
       </c>
       <c r="O15" t="n">
-        <v>20388574940</v>
+        <v>19157350115</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>8850</v>
       </c>
       <c r="Q15" t="n">
-        <v>7300</v>
+        <v>4220</v>
       </c>
       <c r="R15" t="n">
-        <v>-510000</v>
+        <v>-606000</v>
       </c>
       <c r="S15" t="n">
-        <v>19000</v>
+        <v>-8000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 부정적 언급과 함께 FLiPP 투자 시작, 증착기 구매 등 일부 긍정적 기술 투자 내용 포함.</t>
+          <t>금호타이어, 의도적인 주가 누르기에 대한 불만 표출 및 실적 기반 주가 상승 기대. 공매도 문제 지적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['FLiPP', '증착기']</t>
+          <t>['공매도', '영업이익', '호남테마']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12680</v>
+        <v>6850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.37%</t>
+          <t>'-7.56%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.01</v>
+        <v>-0.19</v>
       </c>
       <c r="E16" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13400</v>
+        <v>7410</v>
       </c>
       <c r="K16" t="n">
-        <v>13750</v>
+        <v>7330</v>
       </c>
       <c r="L16" t="n">
-        <v>15390</v>
+        <v>8040</v>
       </c>
       <c r="M16" t="n">
-        <v>12380</v>
+        <v>6830</v>
       </c>
       <c r="N16" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="O16" t="n">
-        <v>176466802570</v>
+        <v>64285033360</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>23500</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>2890</v>
       </c>
       <c r="R16" t="n">
-        <v>-76000</v>
+        <v>-241000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-130000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 투자 이슈와 함께 주가 상승 기대. 단기적 등락 및 테마주 위험성 언급.</t>
+          <t>건설기초소재대장주로 언급되며 수도권 거점 공장 보유. 일부 투자자는 차익 실현 매도를 하였으나, 바닥 지지 및 매집 정황을 근거로 매수 진입을 고려하는 의견도 있음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['호남 반도체', '속도전', '금건']</t>
+          <t>['건설기초소재', '거점공장', '매집']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6870</v>
+        <v>14510</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.29%</t>
+          <t>'-7.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8</v>
+        <v>3.43</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>7410</v>
+        <v>15720</v>
       </c>
       <c r="K17" t="n">
-        <v>7330</v>
+        <v>14770</v>
       </c>
       <c r="L17" t="n">
-        <v>8040</v>
+        <v>15130</v>
       </c>
       <c r="M17" t="n">
-        <v>6850</v>
+        <v>14160</v>
       </c>
       <c r="N17" t="n">
-        <v>1.99</v>
+        <v>3.37</v>
       </c>
       <c r="O17" t="n">
-        <v>63866344820</v>
+        <v>70962237210</v>
       </c>
       <c r="P17" t="n">
-        <v>23500</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>2890</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-241000</v>
+        <v>85000</v>
       </c>
       <c r="S17" t="n">
-        <v>-130000</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>건설기초소재대장주로 언급되며 수도권 거점 공장 보유. 일부 투자자는 차익 실현 매도를 하였으나, 바닥 지지 및 매집 정황을 근거로 매수 진입을 고려하는 의견도 있음.</t>
+          <t>3분기 매출액 668억, 영업이익 59억으로 전분기 대비 어닝 서프라이즈 기록. 미국 업체 광케이블 기술력 하락 언급 및 AI 거품론 우려로 인한 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['건설기초소재', '거점공장', '매집']</t>
+          <t>['어닝서프라이즈', '광케이블', 'AI거품론']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,86 +2028,86 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14570</v>
+        <v>231000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.32%</t>
+          <t>'-7.78%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E18" t="n">
-        <v>111</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>72</v>
+        <v>565</v>
       </c>
       <c r="G18" t="n">
-        <v>366</v>
+        <v>1842</v>
       </c>
       <c r="H18" t="n">
-        <v>3.43</v>
+        <v>46.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>15720</v>
+        <v>250500</v>
       </c>
       <c r="K18" t="n">
-        <v>14770</v>
+        <v>241500</v>
       </c>
       <c r="L18" t="n">
-        <v>15130</v>
+        <v>244000</v>
       </c>
       <c r="M18" t="n">
-        <v>14160</v>
+        <v>228000</v>
       </c>
       <c r="N18" t="n">
-        <v>3.37</v>
+        <v>46.35</v>
       </c>
       <c r="O18" t="n">
-        <v>70050514900</v>
+        <v>3384936745250</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>90200</v>
       </c>
       <c r="R18" t="n">
-        <v>85000</v>
+        <v>-2204000</v>
       </c>
       <c r="S18" t="n">
-        <v>2000</v>
+        <v>241000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3분기 매출액 668억, 영업이익 59억으로 전분기 대비 어닝 서프라이즈 기록. 미국 업체 광케이블 기술력 하락 언급 및 AI 거품론 우려로 인한 주가 하락세 지속.</t>
+          <t>특정 정치인 및 지역 관련 부정적 언급과 함께 주가 하락 및 투자자 이탈 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '광케이블', 'AI거품론']</t>
+          <t>['이재명', '전라도', '포모']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>172800</v>
+        <v>172200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.49%</t>
+          <t>'-7.82%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H19" t="n">
         <v>75.20999999999999</v>
@@ -2174,7 +2174,7 @@
         <v>75.23</v>
       </c>
       <c r="O19" t="n">
-        <v>522643062750</v>
+        <v>534662518050</v>
       </c>
       <c r="P19" t="n">
         <v>243500</v>
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1468000</v>
+        <v>12290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-8.54%</t>
+          <t>'-8.28%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.11</v>
+        <v>-1.01</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>144</v>
       </c>
       <c r="F20" t="n">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="G20" t="n">
-        <v>1652</v>
+        <v>337</v>
       </c>
       <c r="H20" t="n">
-        <v>49.41</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1605000</v>
+        <v>13400</v>
       </c>
       <c r="K20" t="n">
-        <v>1538000</v>
+        <v>13750</v>
       </c>
       <c r="L20" t="n">
-        <v>1554000</v>
+        <v>15390</v>
       </c>
       <c r="M20" t="n">
-        <v>1445000</v>
+        <v>12210</v>
       </c>
       <c r="N20" t="n">
-        <v>49.52</v>
+        <v>1.01</v>
       </c>
       <c r="O20" t="n">
-        <v>4351175384500</v>
+        <v>180535967455</v>
       </c>
       <c r="P20" t="n">
-        <v>2987000</v>
+        <v>19380</v>
       </c>
       <c r="Q20" t="n">
-        <v>403000</v>
+        <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>-722000</v>
+        <v>-76000</v>
       </c>
       <c r="S20" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정치적 논쟁과 특정 인물에 대한 비난이 주를 이루며, 주식 시장 상황에 대한 부정적 인식이 나타남.</t>
+          <t>반도체 관련 속도전 언급 속에서 주가 상승에 대한 기대와 실망감이 교차하며 목표가 달성 실패 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['속도전', '호남 반도체', '목표가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>231500</v>
+        <v>1459000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-11.98%</t>
+          <t>'-9.10%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="E21" t="n">
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="G21" t="n">
-        <v>1849</v>
+        <v>1671</v>
       </c>
       <c r="H21" t="n">
-        <v>46.3</v>
+        <v>49.41</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>263000</v>
+        <v>1605000</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1538000</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1554000</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1445000</v>
       </c>
       <c r="N21" t="n">
-        <v>46.35</v>
+        <v>49.52</v>
       </c>
       <c r="O21" t="n">
-        <v>3312827000000</v>
+        <v>4445955128000</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>403000</v>
       </c>
       <c r="R21" t="n">
-        <v>-2204000</v>
+        <v>-722000</v>
       </c>
       <c r="S21" t="n">
-        <v>241000</v>
+        <v>88000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>정치적 비난과 지역 감정 조장이 주를 이루며, 특정 정치인에 대한 부정적 언급이 다수 포함됨.</t>
+          <t>현 정부 및 특정 정당에 대한 비판과 함께 주가 하락에 대한 좌절감 및 투자자 이탈 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['민주당', '주식시장', '공산좌파']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261013_12.xlsx
+++ b/data/trending_integrated_20261013_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87378380270</v>
+        <v>87446205770</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17700</v>
+        <v>17500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.26%</t>
+          <t>'+7.03%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G3" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>228819553470</v>
+        <v>232123495425</v>
       </c>
       <c r="P3" t="n">
         <v>19930</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 보안주 폭락 속에서도 신고가 돌파 기대감, AI 해킹 관련 기술력 부각 등 긍정적 전망 제시.</t>
+          <t>보안주로서의 강세 및 신고가 돌파 기대감 표출. AI 해킹 관련 뉴스를 근거로 기술적 분석 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3965</v>
+        <v>3880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.87%</t>
+          <t>'+4.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.13</v>
       </c>
       <c r="E4" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H4" t="n">
         <v>0.91</v>
@@ -794,7 +794,7 @@
         <v>0.78</v>
       </c>
       <c r="O4" t="n">
-        <v>81820876305</v>
+        <v>83625326232</v>
       </c>
       <c r="P4" t="n">
         <v>6660</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11580</v>
+        <v>11130</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.61%</t>
+          <t>'+0.54%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.92</v>
       </c>
       <c r="E5" t="n">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="F5" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G5" t="n">
-        <v>331</v>
+        <v>373</v>
       </c>
       <c r="H5" t="n">
         <v>15.64</v>
@@ -880,13 +880,13 @@
         <v>13970</v>
       </c>
       <c r="M5" t="n">
-        <v>11200</v>
+        <v>11130</v>
       </c>
       <c r="N5" t="n">
         <v>14.72</v>
       </c>
       <c r="O5" t="n">
-        <v>313940152890</v>
+        <v>322854795465</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>호남클러스터 외 테마 사망 및 물갈이론 언급, 주가 급등 기대와 계단식 하락 경고 혼재.</t>
+          <t>호남클러스터 외 테마 소멸 및 물량 소화 과정 언급. 일부 매도 및 보유 의견 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주포', '물갈이', '계단식 하락']</t>
+          <t>['호남클러스터', '매도', '물량소화']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13410</v>
+        <v>13270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-1.04%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="H6" t="n">
         <v>0.3</v>
@@ -978,7 +978,7 @@
         <v>0.21</v>
       </c>
       <c r="O6" t="n">
-        <v>61543567335</v>
+        <v>62173104395</v>
       </c>
       <c r="P6" t="n">
         <v>28700</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1568</v>
+        <v>18270</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.63%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.42</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>201</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1578</v>
+        <v>18550</v>
       </c>
       <c r="K7" t="n">
-        <v>1578</v>
+        <v>17550</v>
       </c>
       <c r="L7" t="n">
-        <v>1776</v>
+        <v>19580</v>
       </c>
       <c r="M7" t="n">
-        <v>1457</v>
+        <v>17010</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>0.88</v>
       </c>
       <c r="O7" t="n">
-        <v>8594601303</v>
+        <v>70805460590</v>
       </c>
       <c r="P7" t="n">
-        <v>2930</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>910</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>34000</v>
+        <v>-65000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
+          <t>국내 해킹 이슈 및 보안주 강세 흐름 속에서 엑스게이트 주가 급등 기대감 표출. 매집 의혹 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['경제자유구역', '전국구', '수혜주']</t>
+          <t>['해킹', '보안주', '급등']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18150</v>
+        <v>43300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.16%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.42</v>
+        <v>-0.23</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>197</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="G8" t="n">
-        <v>90</v>
+        <v>663</v>
       </c>
       <c r="H8" t="n">
-        <v>0.46</v>
+        <v>13.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18550</v>
+        <v>44400</v>
       </c>
       <c r="K8" t="n">
-        <v>17550</v>
+        <v>43300</v>
       </c>
       <c r="L8" t="n">
-        <v>19580</v>
+        <v>44100</v>
       </c>
       <c r="M8" t="n">
-        <v>17010</v>
+        <v>42250</v>
       </c>
       <c r="N8" t="n">
-        <v>0.88</v>
+        <v>13.33</v>
       </c>
       <c r="O8" t="n">
-        <v>70451567840</v>
+        <v>24039027050</v>
       </c>
       <c r="P8" t="n">
-        <v>30550</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>6100</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>-65000</v>
+        <v>45000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>국내 해킹 비상 및 프랑스 매장 해킹 사례 언급, 보안주로서의 상승 기대감과 라온시큐어와의 비교 언급.</t>
+          <t>공매도 세력에 대한 경계와 함께 간암 1차 승인 기대감, 악성 매물 소화 필요성 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['해킹', '보안주']</t>
+          <t>['공매도', '간암 1차', '악성 매물']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43250</v>
+        <v>1538</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.59%</t>
+          <t>'-2.53%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.23</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>651</v>
+        <v>212</v>
       </c>
       <c r="H9" t="n">
-        <v>13.1</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>44400</v>
+        <v>1578</v>
       </c>
       <c r="K9" t="n">
-        <v>43300</v>
+        <v>1578</v>
       </c>
       <c r="L9" t="n">
-        <v>44100</v>
+        <v>1776</v>
       </c>
       <c r="M9" t="n">
-        <v>42250</v>
+        <v>1457</v>
       </c>
       <c r="N9" t="n">
-        <v>13.33</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>23670145475</v>
+        <v>8788692151</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>2930</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>910</v>
       </c>
       <c r="R9" t="n">
-        <v>45000</v>
+        <v>34000</v>
       </c>
       <c r="S9" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 경계와 함께 간암 1차 승인 기대감, 악성 매물 소화 필요성 및 주가 하락 우려.</t>
+          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '간암 1차', '악성 매물']</t>
+          <t>['경제자유구역', '전국구', '수혜주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15630</v>
+        <v>17550</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>344</v>
+        <v>287</v>
       </c>
       <c r="H10" t="n">
-        <v>9.630000000000001</v>
+        <v>27.69</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16090</v>
+        <v>18010</v>
       </c>
       <c r="K10" t="n">
-        <v>15190</v>
+        <v>17430</v>
       </c>
       <c r="L10" t="n">
-        <v>15980</v>
+        <v>17840</v>
       </c>
       <c r="M10" t="n">
-        <v>15100</v>
+        <v>17210</v>
       </c>
       <c r="N10" t="n">
-        <v>9.470000000000001</v>
+        <v>27.61</v>
       </c>
       <c r="O10" t="n">
-        <v>47668300015</v>
+        <v>51627473295</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>17210</v>
       </c>
       <c r="R10" t="n">
-        <v>395000</v>
+        <v>681000</v>
       </c>
       <c r="S10" t="n">
-        <v>31000</v>
+        <v>71000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>장 상황 악화 및 도배글에 대한 불만, 금감원 사모펀드 긴급 점검 언급과 함께 주가 하락 우려 제기.</t>
+          <t>FLNG 매출 확대 전망 뉴스 인용 및 목표가 42,000원 언급, 주주 환원 정책 요구 및 현 주가 불만 표출.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['국장', '도배글', '금감원']</t>
+          <t>['FLNG', '매출 전망', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17430</v>
+        <v>15610</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.22%</t>
+          <t>'-2.98%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G11" t="n">
-        <v>286</v>
+        <v>353</v>
       </c>
       <c r="H11" t="n">
-        <v>27.69</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18010</v>
+        <v>16090</v>
       </c>
       <c r="K11" t="n">
-        <v>17430</v>
+        <v>15190</v>
       </c>
       <c r="L11" t="n">
-        <v>17840</v>
+        <v>15980</v>
       </c>
       <c r="M11" t="n">
-        <v>17210</v>
+        <v>15100</v>
       </c>
       <c r="N11" t="n">
-        <v>27.61</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>49849103730</v>
+        <v>48730475835</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>17210</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>681000</v>
+        <v>395000</v>
       </c>
       <c r="S11" t="n">
-        <v>71000</v>
+        <v>31000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 뉴스 인용 및 목표가 42,000원 언급, 주주 환원 정책 요구 및 현 주가 불만 표출.</t>
+          <t>국내 증시 및 건설주 전반의 하락세 속에서 대우건설 주가 하락 우려 및 공매도, 대차해지 관련 논의.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['FLNG', '매출 전망', '목표가']</t>
+          <t>['국장', '하락', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5990</v>
+        <v>6020</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.54%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1530,7 +1530,7 @@
         <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>22547017915</v>
+        <v>22663855715</v>
       </c>
       <c r="P12" t="n">
         <v>11370</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68600</v>
+        <v>69100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.06%</t>
+          <t>'-3.36%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F13" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G13" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="H13" t="n">
         <v>22.1</v>
@@ -1622,7 +1622,7 @@
         <v>22.21</v>
       </c>
       <c r="O13" t="n">
-        <v>130388161500</v>
+        <v>134651605050</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7410</v>
+        <v>7430</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.51%</t>
+          <t>'-4.25%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F14" t="n">
         <v>63</v>
       </c>
       <c r="G14" t="n">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="H14" t="n">
         <v>26.01</v>
@@ -1714,7 +1714,7 @@
         <v>26.37</v>
       </c>
       <c r="O14" t="n">
-        <v>20849576465</v>
+        <v>21240192480</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 부정적 언급과 함께 FLiPP 투자 시작, 증착기 구매 등 일부 긍정적 기술 투자 내용 포함.</t>
+          <t>주가 하락 지속 및 회사 실적 부진에 대한 우려 제기. 상폐 또는 매각 관련 언급과 함께 일부 긍정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['FLiPP', '증착기']</t>
+          <t>['주가하락', '실적', '상폐']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.3</v>
       </c>
       <c r="E15" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F15" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="H15" t="n">
         <v>12.27</v>
@@ -1806,7 +1806,7 @@
         <v>12.57</v>
       </c>
       <c r="O15" t="n">
-        <v>19157350115</v>
+        <v>19358902700</v>
       </c>
       <c r="P15" t="n">
         <v>8850</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>금호타이어, 의도적인 주가 누르기에 대한 불만 표출 및 실적 기반 주가 상승 기대. 공매도 문제 지적.</t>
+          <t>의도적 주가 누르기 및 공매도에 대한 불만 표출. 긍정적 영업이익 및 실적 언급과 함께 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '영업이익', '호남테마']</t>
+          <t>['공매도', '영업이익', '주가상승']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6850</v>
+        <v>6900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-7.56%</t>
+          <t>'-6.88%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.19</v>
       </c>
       <c r="E16" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F16" t="n">
         <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="H16" t="n">
         <v>1.8</v>
@@ -1892,13 +1892,13 @@
         <v>8040</v>
       </c>
       <c r="M16" t="n">
-        <v>6830</v>
+        <v>6820</v>
       </c>
       <c r="N16" t="n">
         <v>1.99</v>
       </c>
       <c r="O16" t="n">
-        <v>64285033360</v>
+        <v>64662921590</v>
       </c>
       <c r="P16" t="n">
         <v>23500</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14510</v>
+        <v>14580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.70%</t>
+          <t>'-7.25%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H17" t="n">
         <v>3.43</v>
@@ -1990,7 +1990,7 @@
         <v>3.37</v>
       </c>
       <c r="O17" t="n">
-        <v>70962237210</v>
+        <v>71998488875</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3분기 매출액 668억, 영업이익 59억으로 전분기 대비 어닝 서프라이즈 기록. 미국 업체 광케이블 기술력 하락 언급 및 AI 거품론 우려로 인한 주가 하락세 지속.</t>
+          <t>3분기 어닝 서프라이즈 및 외인 대량 매수 근거 기반으로 주가 급등 전망. 미국 업체 기술력 하락 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '광케이블', 'AI거품론']</t>
+          <t>['어닝서프라이즈', '외인매수', '공장']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>231000</v>
+        <v>231750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.78%</t>
+          <t>'-7.49%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="G18" t="n">
-        <v>1842</v>
+        <v>1791</v>
       </c>
       <c r="H18" t="n">
         <v>46.3</v>
@@ -2082,7 +2082,7 @@
         <v>46.35</v>
       </c>
       <c r="O18" t="n">
-        <v>3384936745250</v>
+        <v>3505236091750</v>
       </c>
       <c r="P18" t="n">
         <v>374500</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>특정 정치인 및 지역 관련 부정적 언급과 함께 주가 하락 및 투자자 이탈 언급.</t>
+          <t>현 정부 및 특정 지역 반도체 공장 설립 관련 부정적 의견 다수 개진. 정치적 비난 집중.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['이재명', '전라도', '포모']</t>
+          <t>['이재명', '반도체', '전라도']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>172200</v>
+        <v>172300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.82%</t>
+          <t>'-7.76%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G19" t="n">
         <v>121</v>
@@ -2174,7 +2174,7 @@
         <v>75.23</v>
       </c>
       <c r="O19" t="n">
-        <v>534662518050</v>
+        <v>548833835000</v>
       </c>
       <c r="P19" t="n">
         <v>243500</v>
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12290</v>
+        <v>1468000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-8.28%</t>
+          <t>'-8.54%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.01</v>
+        <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>144</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>81</v>
+        <v>578</v>
       </c>
       <c r="G20" t="n">
-        <v>337</v>
+        <v>1727</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>49.41</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>13400</v>
+        <v>1605000</v>
       </c>
       <c r="K20" t="n">
-        <v>13750</v>
+        <v>1538000</v>
       </c>
       <c r="L20" t="n">
-        <v>15390</v>
+        <v>1554000</v>
       </c>
       <c r="M20" t="n">
-        <v>12210</v>
+        <v>1445000</v>
       </c>
       <c r="N20" t="n">
-        <v>1.01</v>
+        <v>49.52</v>
       </c>
       <c r="O20" t="n">
-        <v>180535967455</v>
+        <v>4600074510500</v>
       </c>
       <c r="P20" t="n">
-        <v>19380</v>
+        <v>2987000</v>
       </c>
       <c r="Q20" t="n">
-        <v>3200</v>
+        <v>403000</v>
       </c>
       <c r="R20" t="n">
-        <v>-76000</v>
+        <v>-722000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>반도체 관련 속도전 언급 속에서 주가 상승에 대한 기대와 실망감이 교차하며 목표가 달성 실패 언급.</t>
+          <t>현 정부 정책 및 특정 지역 반도체 공장 투자에 대한 부정적 시각과 함께 주가 하락에 대한 정치적 비난.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['속도전', '호남 반도체', '목표가']</t>
+          <t>['민주당', '반도체', '정치']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,18 +2304,18 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1459000</v>
+        <v>12180</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2323,19 +2323,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.11</v>
+        <v>-1.01</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>148</v>
       </c>
       <c r="F21" t="n">
-        <v>583</v>
+        <v>82</v>
       </c>
       <c r="G21" t="n">
-        <v>1671</v>
+        <v>364</v>
       </c>
       <c r="H21" t="n">
-        <v>49.41</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1605000</v>
+        <v>13400</v>
       </c>
       <c r="K21" t="n">
-        <v>1538000</v>
+        <v>13750</v>
       </c>
       <c r="L21" t="n">
-        <v>1554000</v>
+        <v>15390</v>
       </c>
       <c r="M21" t="n">
-        <v>1445000</v>
+        <v>12120</v>
       </c>
       <c r="N21" t="n">
-        <v>49.52</v>
+        <v>1.01</v>
       </c>
       <c r="O21" t="n">
-        <v>4445955128000</v>
+        <v>183194431670</v>
       </c>
       <c r="P21" t="n">
-        <v>2987000</v>
+        <v>19380</v>
       </c>
       <c r="Q21" t="n">
-        <v>403000</v>
+        <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>-722000</v>
+        <v>-76000</v>
       </c>
       <c r="S21" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>현 정부 및 특정 정당에 대한 비판과 함께 주가 하락에 대한 좌절감 및 투자자 이탈 언급.</t>
+          <t>공매도 및 외인 매매에 대한 부정적 인식과 함께 단기 급등 후 하락에 대한 아쉬움 표출. 목표가 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['민주당', '주식시장', '공산좌파']</t>
+          <t>['공매도', '외인', '목표가']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
